--- a/pa_data.xlsx
+++ b/pa_data.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -17,16 +17,13 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="1">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -37,7 +34,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -45,21 +42,12 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -425,51 +413,51 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I177"/>
+  <dimension ref="A1:I192"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>Year</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>Month_#</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>Practice area</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>Number</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>Research hours</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>Month</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>Effective requests</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>Avg hours</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>Engagement</t>
         </is>
@@ -6281,6 +6269,501 @@
       </c>
       <c r="I177" t="n">
         <v>0.46</v>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" t="n">
+        <v>2026</v>
+      </c>
+      <c r="B178" t="n">
+        <v>1</v>
+      </c>
+      <c r="C178" t="inlineStr">
+        <is>
+          <t>HC</t>
+        </is>
+      </c>
+      <c r="D178" t="n">
+        <v>84</v>
+      </c>
+      <c r="E178" t="n">
+        <v>268</v>
+      </c>
+      <c r="F178" t="inlineStr">
+        <is>
+          <t>Jan</t>
+        </is>
+      </c>
+      <c r="G178" t="n">
+        <v>72</v>
+      </c>
+      <c r="H178" t="n">
+        <v>3.72</v>
+      </c>
+      <c r="I178" t="n">
+        <v>0.23</v>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" t="n">
+        <v>2026</v>
+      </c>
+      <c r="B179" t="n">
+        <v>1</v>
+      </c>
+      <c r="C179" t="inlineStr">
+        <is>
+          <t>IG+EN</t>
+        </is>
+      </c>
+      <c r="D179" t="n">
+        <v>68</v>
+      </c>
+      <c r="E179" t="n">
+        <v>165</v>
+      </c>
+      <c r="F179" t="inlineStr">
+        <is>
+          <t>Jan</t>
+        </is>
+      </c>
+      <c r="G179" t="n">
+        <v>65</v>
+      </c>
+      <c r="H179" t="n">
+        <v>2.54</v>
+      </c>
+      <c r="I179" t="n">
+        <v>0.35</v>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" t="n">
+        <v>2026</v>
+      </c>
+      <c r="B180" t="n">
+        <v>1</v>
+      </c>
+      <c r="C180" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="D180" t="n">
+        <v>36</v>
+      </c>
+      <c r="E180" t="n">
+        <v>101</v>
+      </c>
+      <c r="F180" t="inlineStr">
+        <is>
+          <t>Jan</t>
+        </is>
+      </c>
+      <c r="G180" t="n">
+        <v>22</v>
+      </c>
+      <c r="H180" t="n">
+        <v>4.59</v>
+      </c>
+      <c r="I180" t="n">
+        <v>1.03</v>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" t="n">
+        <v>2026</v>
+      </c>
+      <c r="B181" t="n">
+        <v>1</v>
+      </c>
+      <c r="C181" t="inlineStr">
+        <is>
+          <t>TDA</t>
+        </is>
+      </c>
+      <c r="D181" t="n">
+        <v>20</v>
+      </c>
+      <c r="E181" t="n">
+        <v>40</v>
+      </c>
+      <c r="F181" t="inlineStr">
+        <is>
+          <t>Jan</t>
+        </is>
+      </c>
+      <c r="G181" t="n">
+        <v>19</v>
+      </c>
+      <c r="H181" t="n">
+        <v>2.11</v>
+      </c>
+      <c r="I181" t="n">
+        <v>0.15</v>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" t="n">
+        <v>2026</v>
+      </c>
+      <c r="B182" t="n">
+        <v>1</v>
+      </c>
+      <c r="C182" t="inlineStr">
+        <is>
+          <t>TMT</t>
+        </is>
+      </c>
+      <c r="D182" t="n">
+        <v>62</v>
+      </c>
+      <c r="E182" t="n">
+        <v>153</v>
+      </c>
+      <c r="F182" t="inlineStr">
+        <is>
+          <t>Jan</t>
+        </is>
+      </c>
+      <c r="G182" t="n">
+        <v>53</v>
+      </c>
+      <c r="H182" t="n">
+        <v>2.89</v>
+      </c>
+      <c r="I182" t="n">
+        <v>0.47</v>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" t="n">
+        <v>2026</v>
+      </c>
+      <c r="B183" t="n">
+        <v>2</v>
+      </c>
+      <c r="C183" t="inlineStr">
+        <is>
+          <t>HC</t>
+        </is>
+      </c>
+      <c r="D183" t="n">
+        <v>40</v>
+      </c>
+      <c r="E183" t="n">
+        <v>174</v>
+      </c>
+      <c r="F183" t="inlineStr">
+        <is>
+          <t>Feb</t>
+        </is>
+      </c>
+      <c r="G183" t="n">
+        <v>25</v>
+      </c>
+      <c r="H183" t="n">
+        <v>6.96</v>
+      </c>
+      <c r="I183" t="n">
+        <v>0.92</v>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184" t="n">
+        <v>2026</v>
+      </c>
+      <c r="B184" t="n">
+        <v>2</v>
+      </c>
+      <c r="C184" t="inlineStr">
+        <is>
+          <t>IG+EN</t>
+        </is>
+      </c>
+      <c r="D184" t="n">
+        <v>45</v>
+      </c>
+      <c r="E184" t="n">
+        <v>127</v>
+      </c>
+      <c r="F184" t="inlineStr">
+        <is>
+          <t>Feb</t>
+        </is>
+      </c>
+      <c r="G184" t="n">
+        <v>34</v>
+      </c>
+      <c r="H184" t="n">
+        <v>3.74</v>
+      </c>
+      <c r="I184" t="n">
+        <v>0.5600000000000001</v>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" t="n">
+        <v>2026</v>
+      </c>
+      <c r="B185" t="n">
+        <v>2</v>
+      </c>
+      <c r="C185" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="D185" t="n">
+        <v>19</v>
+      </c>
+      <c r="E185" t="n">
+        <v>76</v>
+      </c>
+      <c r="F185" t="inlineStr">
+        <is>
+          <t>Feb</t>
+        </is>
+      </c>
+      <c r="G185" t="n">
+        <v>2</v>
+      </c>
+      <c r="H185" t="n">
+        <v>38</v>
+      </c>
+      <c r="I185" t="n">
+        <v>1.37</v>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186" t="n">
+        <v>2026</v>
+      </c>
+      <c r="B186" t="n">
+        <v>2</v>
+      </c>
+      <c r="C186" t="inlineStr">
+        <is>
+          <t>TDA</t>
+        </is>
+      </c>
+      <c r="D186" t="n">
+        <v>13</v>
+      </c>
+      <c r="E186" t="n">
+        <v>52</v>
+      </c>
+      <c r="F186" t="inlineStr">
+        <is>
+          <t>Feb</t>
+        </is>
+      </c>
+      <c r="G186" t="n">
+        <v>11</v>
+      </c>
+      <c r="H186" t="n">
+        <v>4.73</v>
+      </c>
+      <c r="I186" t="n">
+        <v>0.54</v>
+      </c>
+    </row>
+    <row r="187">
+      <c r="A187" t="n">
+        <v>2026</v>
+      </c>
+      <c r="B187" t="n">
+        <v>2</v>
+      </c>
+      <c r="C187" t="inlineStr">
+        <is>
+          <t>TMT</t>
+        </is>
+      </c>
+      <c r="D187" t="n">
+        <v>25</v>
+      </c>
+      <c r="E187" t="n">
+        <v>66</v>
+      </c>
+      <c r="F187" t="inlineStr">
+        <is>
+          <t>Feb</t>
+        </is>
+      </c>
+      <c r="G187" t="n">
+        <v>16</v>
+      </c>
+      <c r="H187" t="n">
+        <v>4.12</v>
+      </c>
+      <c r="I187" t="n">
+        <v>1.12</v>
+      </c>
+    </row>
+    <row r="188">
+      <c r="A188" t="n">
+        <v>2026</v>
+      </c>
+      <c r="B188" t="n">
+        <v>3</v>
+      </c>
+      <c r="C188" t="inlineStr">
+        <is>
+          <t>HC</t>
+        </is>
+      </c>
+      <c r="D188" t="n">
+        <v>39</v>
+      </c>
+      <c r="E188" t="n">
+        <v>150</v>
+      </c>
+      <c r="F188" t="inlineStr">
+        <is>
+          <t>Mar</t>
+        </is>
+      </c>
+      <c r="G188" t="n">
+        <v>27</v>
+      </c>
+      <c r="H188" t="n">
+        <v>5.56</v>
+      </c>
+      <c r="I188" t="n">
+        <v>0.64</v>
+      </c>
+    </row>
+    <row r="189">
+      <c r="A189" t="n">
+        <v>2026</v>
+      </c>
+      <c r="B189" t="n">
+        <v>3</v>
+      </c>
+      <c r="C189" t="inlineStr">
+        <is>
+          <t>IG+EN</t>
+        </is>
+      </c>
+      <c r="D189" t="n">
+        <v>15</v>
+      </c>
+      <c r="E189" t="n">
+        <v>49</v>
+      </c>
+      <c r="F189" t="inlineStr">
+        <is>
+          <t>Mar</t>
+        </is>
+      </c>
+      <c r="G189" t="n">
+        <v>7</v>
+      </c>
+      <c r="H189" t="n">
+        <v>7</v>
+      </c>
+      <c r="I189" t="n">
+        <v>1.2</v>
+      </c>
+    </row>
+    <row r="190">
+      <c r="A190" t="n">
+        <v>2026</v>
+      </c>
+      <c r="B190" t="n">
+        <v>3</v>
+      </c>
+      <c r="C190" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="D190" t="n">
+        <v>15</v>
+      </c>
+      <c r="E190" t="n">
+        <v>42.5</v>
+      </c>
+      <c r="F190" t="inlineStr">
+        <is>
+          <t>Mar</t>
+        </is>
+      </c>
+      <c r="G190" t="n">
+        <v>6</v>
+      </c>
+      <c r="H190" t="n">
+        <v>7.08</v>
+      </c>
+      <c r="I190" t="n">
+        <v>2.33</v>
+      </c>
+    </row>
+    <row r="191">
+      <c r="A191" t="n">
+        <v>2026</v>
+      </c>
+      <c r="B191" t="n">
+        <v>3</v>
+      </c>
+      <c r="C191" t="inlineStr">
+        <is>
+          <t>TDA</t>
+        </is>
+      </c>
+      <c r="D191" t="n">
+        <v>12</v>
+      </c>
+      <c r="E191" t="n">
+        <v>34</v>
+      </c>
+      <c r="F191" t="inlineStr">
+        <is>
+          <t>Mar</t>
+        </is>
+      </c>
+      <c r="G191" t="n">
+        <v>9</v>
+      </c>
+      <c r="H191" t="n">
+        <v>3.78</v>
+      </c>
+      <c r="I191" t="n">
+        <v>0.33</v>
+      </c>
+    </row>
+    <row r="192">
+      <c r="A192" t="n">
+        <v>2026</v>
+      </c>
+      <c r="B192" t="n">
+        <v>3</v>
+      </c>
+      <c r="C192" t="inlineStr">
+        <is>
+          <t>TMT</t>
+        </is>
+      </c>
+      <c r="D192" t="n">
+        <v>20</v>
+      </c>
+      <c r="E192" t="n">
+        <v>54</v>
+      </c>
+      <c r="F192" t="inlineStr">
+        <is>
+          <t>Mar</t>
+        </is>
+      </c>
+      <c r="G192" t="n">
+        <v>13</v>
+      </c>
+      <c r="H192" t="n">
+        <v>4.15</v>
+      </c>
+      <c r="I192" t="n">
+        <v>2.25</v>
       </c>
     </row>
   </sheetData>
